--- a/AAII_Financials/Yearly/MAA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MAA_YR_FIN.xlsx
@@ -1008,13 +1008,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-22200</v>
+        <v>-15700</v>
       </c>
       <c r="E14" s="3">
-        <v>-65700</v>
+        <v>-52600</v>
       </c>
       <c r="F14" s="3">
-        <v>-7300</v>
+        <v>-5700</v>
       </c>
       <c r="G14" s="3">
         <v>-205600</v>
@@ -1251,13 +1251,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4800</v>
+        <v>-11300</v>
       </c>
       <c r="E20" s="3">
-        <v>7100</v>
+        <v>-6000</v>
       </c>
       <c r="F20" s="3">
-        <v>-25600</v>
+        <v>-27200</v>
       </c>
       <c r="G20" s="3">
         <v>31100</v>
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1246500</v>
+        <v>1253000</v>
       </c>
       <c r="E21" s="3">
-        <v>1235300</v>
+        <v>1248400</v>
       </c>
       <c r="F21" s="3">
-        <v>1279500</v>
+        <v>1281100</v>
       </c>
       <c r="G21" s="3">
         <v>1140700</v>
@@ -1863,13 +1863,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4800</v>
+        <v>11300</v>
       </c>
       <c r="E32" s="3">
-        <v>-7100</v>
+        <v>6000</v>
       </c>
       <c r="F32" s="3">
-        <v>25600</v>
+        <v>27200</v>
       </c>
       <c r="G32" s="3">
         <v>-31100</v>
